--- a/data/trans_bre/IP04D$colectiva-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$colectiva-Edad-trans_bre.xlsx
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 6,82</t>
+          <t>-0,97; 6,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 6,4</t>
+          <t>-0,9; 5,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 5,39</t>
+          <t>-6,56; 4,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-31,9; 480,81</t>
+          <t>-31,19; 597,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-41,47; —</t>
+          <t>-52,66; inf</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-66,04; 132,62</t>
+          <t>-65,66; 114,35</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 1,39</t>
+          <t>-3,6; 1,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 2,8</t>
+          <t>-2,47; 2,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 6,36</t>
+          <t>-2,35; 6,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-78,19; 80,2</t>
+          <t>-73,71; 89,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-57,29; 140,3</t>
+          <t>-56,78; 147,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-30,8; 166,21</t>
+          <t>-34,25; 165,62</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 3,45</t>
+          <t>-2,7; 3,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 3,89</t>
+          <t>-2,31; 3,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 4,87</t>
+          <t>-5,22; 4,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-66,99; 238,28</t>
+          <t>-70,58; 231,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-56,48; 321,78</t>
+          <t>-58,03; 303,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-46,79; 78,39</t>
+          <t>-50,62; 71,54</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 4,8</t>
+          <t>-0,52; 5,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 0,5</t>
+          <t>-7,11; 0,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 5,43</t>
+          <t>-2,56; 4,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-40,22; 1199,48</t>
+          <t>-43,23; 985,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-82,21; 24,86</t>
+          <t>-83,48; 21,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,55; 115,46</t>
+          <t>-31,86; 94,98</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 2,22</t>
+          <t>-0,74; 2,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 1,54</t>
+          <t>-1,76; 1,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 3,37</t>
+          <t>-1,51; 3,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-22,07; 98,45</t>
+          <t>-22,76; 108,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-39,14; 53,53</t>
+          <t>-40,08; 53,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-19,82; 56,01</t>
+          <t>-20,58; 55,47</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04D$colectiva-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$colectiva-Edad-trans_bre.xlsx
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 6,69</t>
+          <t>-1,02; 6,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 5,57</t>
+          <t>-0,59; 6,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 4,95</t>
+          <t>-7,01; 5,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-31,19; 597,49</t>
+          <t>-34,08; 468,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-52,66; inf</t>
+          <t>-39,26; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-65,66; 114,35</t>
+          <t>-67,57; 132,65</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 1,62</t>
+          <t>-3,56; 1,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 2,87</t>
+          <t>-2,56; 2,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 6,5</t>
+          <t>-2,3; 6,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-73,71; 89,64</t>
+          <t>-75,3; 89,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-56,78; 147,41</t>
+          <t>-54,11; 151,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-34,25; 165,62</t>
+          <t>-32,27; 168,36</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 3,54</t>
+          <t>-2,95; 3,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 3,82</t>
+          <t>-2,84; 3,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 4,48</t>
+          <t>-5,03; 4,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-70,58; 231,45</t>
+          <t>-65,29; 233,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-58,03; 303,66</t>
+          <t>-64,81; 223,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-50,62; 71,54</t>
+          <t>-47,13; 72,91</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 5,1</t>
+          <t>-0,57; 4,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 0,43</t>
+          <t>-6,84; 0,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 4,92</t>
+          <t>-2,59; 4,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-43,23; 985,88</t>
+          <t>-39,5; 779,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-83,48; 21,27</t>
+          <t>-83,57; 35,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,86; 94,98</t>
+          <t>-33,34; 98,64</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 2,31</t>
+          <t>-0,69; 2,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 1,55</t>
+          <t>-1,76; 1,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 3,29</t>
+          <t>-1,32; 3,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-22,76; 108,39</t>
+          <t>-22,18; 96,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-40,08; 53,79</t>
+          <t>-38,89; 53,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-20,58; 55,47</t>
+          <t>-16,81; 54,31</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04D$colectiva-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$colectiva-Edad-trans_bre.xlsx
@@ -518,8 +518,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que dispone de calefacción colectiva en su vivienda</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -604,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,72</t>
+          <t>-0,07</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -619,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-9,77%</t>
+          <t>-1,08%</t>
         </is>
       </c>
     </row>
@@ -632,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 6,83</t>
+          <t>-0,96; 6,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 6,13</t>
+          <t>-0,75; 6,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 5,68</t>
+          <t>-5,4; 5,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-34,08; 468,75</t>
+          <t>-31,9; 480,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-39,26; —</t>
+          <t>-41,47; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-67,57; 132,65</t>
+          <t>-63,31; 150,74</t>
         </is>
       </c>
     </row>
@@ -684,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,11</t>
+          <t>2,96</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -699,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>54,53%</t>
         </is>
       </c>
     </row>
@@ -712,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 1,52</t>
+          <t>-3,84; 1,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 2,97</t>
+          <t>-2,35; 2,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 6,68</t>
+          <t>-1,23; 7,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-75,3; 89,7</t>
+          <t>-78,19; 80,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-54,11; 151,39</t>
+          <t>-57,29; 140,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-32,27; 168,36</t>
+          <t>-22,11; 190,02</t>
         </is>
       </c>
     </row>
@@ -764,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,37</t>
+          <t>-0,24</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -779,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-4,36%</t>
+          <t>-2,85%</t>
         </is>
       </c>
     </row>
@@ -792,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 3,35</t>
+          <t>-2,97; 3,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 3,45</t>
+          <t>-2,12; 3,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 4,53</t>
+          <t>-4,75; 4,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-65,29; 233,3</t>
+          <t>-66,99; 238,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-64,81; 223,07</t>
+          <t>-56,48; 321,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-47,13; 72,91</t>
+          <t>-46,23; 79,1</t>
         </is>
       </c>
     </row>
@@ -844,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,4</t>
+          <t>2,52</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -859,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>38,95%</t>
         </is>
       </c>
     </row>
@@ -872,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 4,74</t>
+          <t>-0,53; 4,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 0,76</t>
+          <t>-6,92; 0,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 4,94</t>
+          <t>-1,02; 6,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-39,5; 779,4</t>
+          <t>-40,22; 1199,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-83,57; 35,76</t>
+          <t>-82,21; 24,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-33,34; 98,64</t>
+          <t>-16,67; 148,64</t>
         </is>
       </c>
     </row>
@@ -924,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,9</t>
+          <t>1,62</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -939,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>23,81%</t>
         </is>
       </c>
     </row>
@@ -952,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 2,18</t>
+          <t>-0,71; 2,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 1,44</t>
+          <t>-1,65; 1,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 3,39</t>
+          <t>-0,86; 4,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-22,18; 96,86</t>
+          <t>-22,07; 98,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-38,89; 53,49</t>
+          <t>-39,14; 53,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,81; 54,31</t>
+          <t>-11,29; 70,32</t>
         </is>
       </c>
     </row>
